--- a/data/source_trackers/UK_2027_Summer_Internship_Trackr_Master.xlsx
+++ b/data/source_trackers/UK_2027_Summer_Internship_Trackr_Master.xlsx
@@ -846,7 +846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1894,62 +1894,63 @@
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="17" t="n">
+      <c r="A18" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>L2 Tier</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>Castleton Commodities (CCI)</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>Data Engineering Internship (Summer 2027)</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="inlineStr">
-        <is>
-          <t>Trackr UK Tech</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Virtu Financial</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>2027 Summer Internship - Technical</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>기업 공식포털 단독발굴
+(Trackr 누락)</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Tech / Quant Systems</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
         <is>
           <t>London, UK</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H18" s="15" t="inlineStr">
         <is>
           <t>Penultimate (2028 졸)</t>
         </is>
       </c>
-      <c r="I18" s="21" t="inlineStr">
+      <c r="I18" s="15" t="inlineStr">
         <is>
           <t>Rolling</t>
         </is>
       </c>
-      <c r="J18" s="18" t="inlineStr">
+      <c r="J18" s="12" t="inlineStr">
         <is>
           <t>To-Apply (L2)</t>
         </is>
       </c>
-      <c r="K18" s="22" t="inlineStr">
+      <c r="K18" s="16" t="inlineStr">
         <is>
           <t>바로 지원하기 ↗</t>
         </is>
       </c>
-      <c r="L18" s="19" t="inlineStr">
-        <is>
-          <t>글로벌 원자재 및 에너지 트레이딩 빅데이터 파이프라인 개발.</t>
+      <c r="L18" s="13" t="inlineStr">
+        <is>
+          <t>글로벌 마켓메이커 기술 인프라 및 트레이딩 시스템 엔지니어링.</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1965,12 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Virtu Financial</t>
+          <t>Maven Securities</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>2027 Summer Internship - Technical</t>
+          <t>London Trader Summer Internship 2027</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
@@ -1980,7 +1981,7 @@
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Tech / Quant Systems</t>
+          <t>Quant Trading</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
@@ -1995,7 +1996,7 @@
       </c>
       <c r="I19" s="15" t="inlineStr">
         <is>
-          <t>Rolling</t>
+          <t>2026-10-21 마감</t>
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr">
@@ -2010,7 +2011,7 @@
       </c>
       <c r="L19" s="13" t="inlineStr">
         <is>
-          <t>글로벌 마켓메이커 기술 인프라 및 트레이딩 시스템 엔지니어링.</t>
+          <t>런던 파생상품 마켓메이킹 알고리즘 및 트레이딩 데스크 실무.</t>
         </is>
       </c>
     </row>
@@ -2025,12 +2026,12 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Maven Securities</t>
+          <t>The Technology Partnership (TTP)</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>London Trader Summer Internship 2027</t>
+          <t>Summer Internship - Electronic Engineering Consultant</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
@@ -2041,12 +2042,12 @@
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>Quant Trading</t>
+          <t>Tech Consulting / Hardware</t>
         </is>
       </c>
       <c r="G20" s="15" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Melbourn, UK</t>
         </is>
       </c>
       <c r="H20" s="15" t="inlineStr">
@@ -2056,7 +2057,7 @@
       </c>
       <c r="I20" s="15" t="inlineStr">
         <is>
-          <t>2026-10-21 마감</t>
+          <t>Rolling</t>
         </is>
       </c>
       <c r="J20" s="12" t="inlineStr">
@@ -2071,71 +2072,11 @@
       </c>
       <c r="L20" s="13" t="inlineStr">
         <is>
-          <t>런던 파생상품 마켓메이킹 알고리즘 및 트레이딩 데스크 실무.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>L2 Tier</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>The Technology Partnership (TTP)</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>Summer Internship - Electronic Engineering Consultant</t>
-        </is>
-      </c>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>기업 공식포털 단독발굴
-(Trackr 누락)</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>Tech Consulting / Hardware</t>
-        </is>
-      </c>
-      <c r="G21" s="15" t="inlineStr">
-        <is>
-          <t>Melbourn, UK</t>
-        </is>
-      </c>
-      <c r="H21" s="15" t="inlineStr">
-        <is>
-          <t>Penultimate (2028 졸)</t>
-        </is>
-      </c>
-      <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>Rolling</t>
-        </is>
-      </c>
-      <c r="J21" s="12" t="inlineStr">
-        <is>
-          <t>To-Apply (L2)</t>
-        </is>
-      </c>
-      <c r="K21" s="16" t="inlineStr">
-        <is>
-          <t>바로 지원하기 ↗</t>
-        </is>
-      </c>
-      <c r="L21" s="13" t="inlineStr">
-        <is>
           <t>헬스케어 및 메디컬 디바이스, 바이오 센서 하드웨어 프로토타이핑 컨설팅.</t>
         </is>
       </c>
     </row>
+    <row r="21" ht="24" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
@@ -2154,10 +2095,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/source_trackers/UK_2027_Summer_Internship_Trackr_Master.xlsx
+++ b/data/source_trackers/UK_2027_Summer_Internship_Trackr_Master.xlsx
@@ -2095,8 +2095,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
